--- a/daily_matches/job_matches_2026-07-22.xlsx
+++ b/daily_matches/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>RAG, Synapse, Git, Databricks, Kafka, Hadoop, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257f59c1e32a324b</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technology Engineer Sr (DevOps/Linux, Web/Application servers, CI/CD )</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MySQL, MongoDB</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e572086521c6face</t>
+          <t>https://www.indeed.com/viewjob?jk=3a63725107df69e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring/SQL)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Athena, CI/CD, Terraform, Git, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,124 +601,124 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist - Applied AI/ML Senior Associate</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db6032672ea4e97</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Business Solutions</t>
+          <t>Data Engineer (GCP, BigQuery)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vertex Service Partners</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, BigQuery, Data Lake, AKS, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e969c03c2beb3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f34e8802feac0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, S3, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=549b6d84346bde29</t>
+          <t>https://www.indeed.com/viewjob?jk=5d759446a8dbf628</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24afdf8094fcbe03</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20f982c8cf710692</t>
+          <t>https://www.indeed.com/viewjob?jk=f91b573ae3948a10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Agent Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Pitt Ohio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee379c221d450f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd581e585d7d8b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d674fa8df62555e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff80308799a14cd2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Engineer 2, Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, S3, Redshift, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04dd605f7e6b4f24</t>
+          <t>https://www.indeed.com/viewjob?jk=4f51f80f51cf91a7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>smart contract engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>DRW Trading Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,252 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=274f0a30f871228a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cloud Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Opti9 Technologies</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5904a80c080601d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Forward Deployed AI Engineer (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e236ddc1d324629a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer- Infrastructure</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e772617aae55e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Python Engineer, Series B Startup</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51e030c34ceb5344</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Backend Engineer, Series B Startup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a81f6a960db881</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Engineer- AI-Driven Analytics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SambaSafety</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Snowflake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99180781fcd20bb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40314dc9daa409d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7b903aa3de4d3c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-22.xlsx
+++ b/daily_matches/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Git, Databricks, Kafka, Hadoop, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a63725107df69e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Kubernetes, Git, Databricks, Python, SQL</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, BigQuery)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, BigQuery, Data Lake, AKS, BigQuery, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f34e8802feac0</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d759446a8dbf628</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91b573ae3948a10</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Agent Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pitt Ohio</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd581e585d7d8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,77 +881,3402 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff80308799a14cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer 2, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f51f80f51cf91a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>smart contract engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DRW Trading Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98bbb8cd3d4b817e</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Frontline Education</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33778df2c46ff386</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Architect – Manufacturing Test</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Mastronardi Produce</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Livonia, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23fb94d56b86606</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4db8a84f40d2c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer AI Agentic Engineer CT &amp; TX</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IPolarity LLC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7b903aa3de4d3c</t>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>S3, Glue, Redshift, Databricks, Redshift, PySpark, Tableau, Python, R</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97db7cca45ac78b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Applied AI, Forward Deployed Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, Mistral, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac298393b4aa963e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DualEntry</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, Terraform, Git, Cassandra, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=867f132c79a5bea8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sonar</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67612aebf856fdc3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-22.xlsx
+++ b/daily_matches/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2378720</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Redshift, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
+          <t>Generative AI, RAG, Cortex, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba77f8c3e7eac143</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Java Microservices Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Data Lake, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e170e5d541b6f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Analytics Engineer (AI Insurance SaaS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f178ece3a91c11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Native, Tech Ops Engineer</t>
+          <t>Software Engineer II, Frontend/AI Fullstack - Growth Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConsumerAffairs</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>LangChain, RAG, FastAPI, Kubernetes, AKS, Snowflake, Databricks, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0dfb62954d95371</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Ops / DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>S3, EC2, Data Lake, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
+          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[C] Data Engineer, Safeguards</t>
+          <t>Software Engineer III (AI/ML)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Git, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Cassandra, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623cec7f1ca0a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecddf74d5b2eb97b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Continuous Improvement</t>
+          <t>Software Engineer II -AI Platform {Teacher Assistant)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fairbanks Morse Defense</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Beloit, WI, US USA</t>
+          <t>Ohio City, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Power BI</t>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ba62e3d62d7b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca75c0d016a854a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Platform Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Speria</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, AWS SageMaker, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6698ae70773b9b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c619303bde5b185</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Test &amp; Infrastructure III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Vail Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85f16e782e81d5</t>
+          <t>https://www.indeed.com/viewjob?jk=19bfee781688b122</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Software Engineer II Platform, Core Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Apache Airflow, CI/CD, Snowflake, PySpark, Tableau, Power BI, R</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699a810448276fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=0969c0d56d36c09c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior AI Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Speria</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, MLflow, Docker, CI/CD, Git, Databricks, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2956b61e4ba6c75</t>
+          <t>https://www.indeed.com/viewjob?jk=37ed07531a5c2bae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist - Customer One</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aguadilla, PR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36862d2a00572334</t>
+          <t>https://www.indeed.com/viewjob?jk=82e171970133e039</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Cloud and AI App Innovation Customer Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JDA TSG</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68ca9d0eb731233</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa2ba2948ba82fd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>Connected Vehicle Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northampton, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, Kinesis, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, CI/CD, Git, BigQuery, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f9bed15db76e45</t>
+          <t>https://www.indeed.com/viewjob?jk=bb20d47584b5712d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, A/B Testing</t>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a872d4a2e4343acf</t>
+          <t>https://www.indeed.com/viewjob?jk=607adef80cc097cb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Developer II - Financials (Full Stack, Front End)</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, Git, Databricks, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, Snowflake, BigQuery, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a143ead9f5447346</t>
+          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer II - Financials (Full Stack, Front End)</t>
+          <t>Senior IAM Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, Git, Databricks, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355c4a87b294a9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5408cc8efa44438c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer II - Financials (Full Stack, Front End)</t>
+          <t>Senior IAM Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, Git, Databricks, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87285cfde95e5fad</t>
+          <t>https://www.indeed.com/viewjob?jk=51f23d8499bda258</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Manufacturing Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>TriMas Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Julia, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a779e1eb2d14245a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d95a29ce8f56c88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Sr. Engineer - Database Engineering (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>East Granby, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9403d161b766c5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a7fab843c617ff</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - Remote (Central Time Zone)</t>
+          <t>Analytics Engineer, Service Parts</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,192 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Gemini, Redshift, Databricks, Redshift, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=540449fb67e9c13e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, Hadoop, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7dc3fdad8aa6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7567aa73dfc07a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer .Net/AI Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Rippling</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD, Git, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c109cc80608f152e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>KL Software Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c79bf944c1ff774</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Business Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BD</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Summit, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d50514b3b5cc2acc</t>
+          <t>https://www.indeed.com/viewjob?jk=3016b5e5d4a7d855</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-22.xlsx
+++ b/daily_matches/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Conduit services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, FastAPI</t>
+          <t>Generative AI, Cortex, S3, Data Lake, Kinesis, Docker, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba77f8c3e7eac143</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1b649e399da37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Microservices Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e170e5d541b6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3aada6e7b7a0a352</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (AI Insurance SaaS)</t>
+          <t>Senior AI Engineer, Applied AI Solutions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EvolutionIQ</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, BigQuery, Docker, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f178ece3a91c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba80bfc109aec2f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II, Frontend/AI Fullstack - Growth Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Marlboro, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, Kubernetes, AKS, Snowflake, Databricks, Kafka, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, Git, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0dfb62954d95371</t>
+          <t>https://www.indeed.com/viewjob?jk=23d224fc86dd31d3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer (Full Stack) - Raise</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Virtuous Software</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Data Lake, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b85b4dba14269c0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III (AI/ML)</t>
+          <t>Senior Solutions Architect, Agentic AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Cassandra, Python, R, Java</t>
+          <t>LangChain, RAG, LLaMA, PyTorch, Kubernetes, CI/CD, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecddf74d5b2eb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=c966cb803cd1cd9b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II -AI Platform {Teacher Assistant)</t>
+          <t>Backend Engineer/Data Engineer/Aspiring AI Generalist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Wider Security LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ohio City, OH, US USA</t>
+          <t>Newport, RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca75c0d016a854a</t>
+          <t>https://www.indeed.com/viewjob?jk=da73b50279ff0b8d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Platform Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, AWS SageMaker, Git, Python, R</t>
+          <t>MLflow, Docker, Databricks, PySpark, Kafka, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c619303bde5b185</t>
+          <t>https://www.indeed.com/viewjob?jk=87068c1cc4a7e538</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Test &amp; Infrastructure III</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vail Systems</t>
+          <t>SANTEE COOPER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Moncks Corner, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bfee781688b122</t>
+          <t>https://www.indeed.com/viewjob?jk=5384d191c57a074d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II Platform, Core Services</t>
+          <t>Machine Learning Scientist II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>Data Scientist, RAG, PySpark, Python, SQL, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0969c0d56d36c09c</t>
+          <t>https://www.indeed.com/viewjob?jk=1220786d2328c639</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Platform Engineer</t>
+          <t>Software Developer II - Connect Service Software (Front End, Billing Software)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ed07531a5c2bae</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a7698337d0c69e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist - Customer One</t>
+          <t>Software Developer II - Connect Service Software (Front End, Billing Software)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Iowa City, IA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Databricks, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e171970133e039</t>
+          <t>https://www.indeed.com/viewjob?jk=50a1eeec3d96a017</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer II - Connect Service Software (Front End, Billing Software)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa2ba2948ba82fd</t>
+          <t>https://www.indeed.com/viewjob?jk=22c83f14e721ae8f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Connected Vehicle Data Engineer</t>
+          <t>BIM Integration Developer - Kiewit Infrastructure Engineers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, CI/CD, Git, BigQuery, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb20d47584b5712d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e389349409a16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>University Federal Credit Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Data Lake, Databricks, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607adef80cc097cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cfb563279695cc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior DevOps Build Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SAI360</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Snowflake, BigQuery, Kafka, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
+          <t>https://www.indeed.com/viewjob?jk=ea26704e7d1e3d66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IAM Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Bishs RV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5408cc8efa44438c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffff7bb6d11de8d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IAM Engineer</t>
+          <t>QE Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f23d8499bda258</t>
+          <t>https://www.indeed.com/viewjob?jk=cf751a8cb9bbc437</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manufacturing Data Scientist</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TriMas Corporation</t>
+          <t>TaylorMade Golf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Julia, Optimization</t>
+          <t>RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d95a29ce8f56c88</t>
+          <t>https://www.indeed.com/viewjob?jk=0271c41b96cbb033</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Database Engineering (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, SQL, R</t>
+          <t>Data Scientist, RAG, Hugging Face, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a7fab843c617ff</t>
+          <t>https://www.indeed.com/viewjob?jk=359f68a27bdf7092</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Service Parts</t>
+          <t>Data Scientist, Growth Marketing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,157 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gemini, Redshift, Databricks, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3016b5e5d4a7d855</t>
+          <t>https://www.indeed.com/viewjob?jk=483786d85359bc55</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a55959fd562b66</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07abae92e023036d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Marketing Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>World Wellness Clubs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boynton Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0800ea5d980369fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Advanced Manufacturing Engineer – Digital Manufacturing Implementation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Northford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c28d94dcb62cdc7a</t>
         </is>
       </c>
     </row>
